--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ82"/>
+  <dimension ref="A1:AJ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10362,8 +10362,1658 @@
       <c r="AI82" s="2" t="inlineStr"/>
       <c r="AJ82" s="2" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>dd2cf74e417f4cee</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>401841470</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>0.300300</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>0.155835</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:29.596146Z</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=dd2cf74e417f4cee;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="2" t="inlineStr"/>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="2" t="inlineStr"/>
+      <c r="AJ83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>bcd0c74dea2043e0</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>0.229885</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>0.168154</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:29.646850Z</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=bcd0c74dea2043e0;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="2" t="inlineStr"/>
+      <c r="AH84" s="2" t="inlineStr"/>
+      <c r="AI84" s="2" t="inlineStr"/>
+      <c r="AJ84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>e13c238530584bba</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>0.469484</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>0.066432</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:30.158682Z</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=e13c238530584bba;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="2" t="inlineStr"/>
+      <c r="AH85" s="2" t="inlineStr"/>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>bf349d7ef19d46ba</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0.370370</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>0.085765</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:31.355163Z</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=bf349d7ef19d46ba;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="2" t="inlineStr"/>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="2" t="inlineStr"/>
+      <c r="AJ86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>edbb690717cf438f</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0.400000</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>0.056135</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:32.444165Z</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr"/>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=edbb690717cf438f;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="2" t="inlineStr"/>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="2" t="inlineStr"/>
+      <c r="AJ87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>fc86e21c33c74db3</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.145291</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:34.034224Z</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=fc86e21c33c74db3;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="2" t="inlineStr"/>
+      <c r="AH88" s="2" t="inlineStr"/>
+      <c r="AI88" s="2" t="inlineStr"/>
+      <c r="AJ88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>1b0da72fb3a74ffe</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>0.190000</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>0.330033</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>0.076644</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:36.285171Z</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr"/>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/picks.xlsx;original_pick_id=1b0da72fb3a74ffe;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="2" t="inlineStr"/>
+      <c r="AH89" s="2" t="inlineStr"/>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>757b695c57d048d8</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>401844015</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>0.450450</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.005685</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:30.754443Z</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr"/>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=757b695c57d048d8;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="2" t="inlineStr"/>
+      <c r="AH90" s="2" t="inlineStr"/>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>3ee247cbcde54b33</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>0.460829</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:31.317492Z</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=3ee247cbcde54b33;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="2" t="inlineStr"/>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="2" t="inlineStr"/>
+      <c r="AJ91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2f2115f499b54b3c</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>0.509804</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>-0.053669</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:31.887658Z</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr"/>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=2f2115f499b54b3c;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="2" t="inlineStr"/>
+      <c r="AH92" s="2" t="inlineStr"/>
+      <c r="AI92" s="2" t="inlineStr"/>
+      <c r="AJ92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>14f7b83e36f147da</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>0.460829</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:32.970430Z</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=14f7b83e36f147da;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="2" t="inlineStr"/>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="2" t="inlineStr"/>
+      <c r="AJ93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>a5e17c7080d24e2b</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>0.190000</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>0.640288</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>-0.225494</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:33.999302Z</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=a5e17c7080d24e2b;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="2" t="inlineStr"/>
+      <c r="AH94" s="2" t="inlineStr"/>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>d986ae8077ec4c9e</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>0.200000</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>0.659864</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>-0.203729</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:35.744825Z</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=d986ae8077ec4c9e;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="2" t="inlineStr"/>
+      <c r="AH95" s="2" t="inlineStr"/>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>73e5fffe29124687</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>401897751</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>0.395592</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>0.040000</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>0.509804</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>-0.114212</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:37.855949Z</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:00Z</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=73e5fffe29124687;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="2" t="inlineStr"/>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="2" t="inlineStr"/>
+      <c r="AJ96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>a724d46587fc4f4c</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>0.040000</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>0.579832</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>-0.096840</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:38.357498Z</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/flat_picks.xlsx;original_pick_id=a724d46587fc4f4c;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="2" t="inlineStr"/>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="2" t="inlineStr"/>
+      <c r="AJ97" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ82"/>
+  <autoFilter ref="A1:AJ97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ97"/>
+  <dimension ref="A1:AJ111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2253,19 +2253,19 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T02:41:46.978948Z</t>
+          <t>2026-08-02T16:18:12.975588Z</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr"/>
@@ -2741,19 +2741,19 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29T02:41:49.507236Z</t>
+          <t>2026-08-02T16:18:13.023433Z</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr"/>
@@ -3107,19 +3107,19 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="inlineStr"/>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T04:12:52.241515Z</t>
+          <t>2026-08-02T16:18:13.069113Z</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr"/>
@@ -3351,19 +3351,19 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30T04:12:52.435602Z</t>
+          <t>2026-08-02T16:18:13.114564Z</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr"/>
@@ -4449,19 +4449,19 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31T21:03:36.213553Z</t>
+          <t>2026-08-02T16:18:13.160687Z</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr"/>
@@ -4937,19 +4937,19 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="inlineStr"/>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T18:35:32.929288Z</t>
+          <t>2026-08-02T16:18:13.205573Z</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr"/>
@@ -5059,19 +5059,19 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="inlineStr"/>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.2500</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T18:35:34.883257Z</t>
+          <t>2026-08-02T16:18:13.256241Z</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr"/>
@@ -5181,19 +5181,19 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="inlineStr"/>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T20:34:14.764038Z</t>
+          <t>2026-08-02T16:18:13.301628Z</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr"/>
@@ -5425,19 +5425,19 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="inlineStr"/>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T21:25:27.602390Z</t>
+          <t>2026-08-02T16:18:13.348287Z</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr"/>
@@ -5547,19 +5547,19 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01T20:13:20.615731Z</t>
+          <t>2026-08-02T16:18:13.393362Z</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr"/>
@@ -6539,19 +6539,19 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr"/>
       <c r="AA50" s="2" t="inlineStr"/>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.0000</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:26:15.055587Z</t>
+          <t>2026-08-02T16:18:13.438877Z</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr"/>
@@ -6783,19 +6783,19 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr"/>
       <c r="AA52" s="2" t="inlineStr"/>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-2.0000</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:26:15.417178Z</t>
+          <t>2026-08-02T16:18:13.484411Z</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr"/>
@@ -8397,19 +8397,19 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr"/>
       <c r="AA65" s="2" t="inlineStr"/>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.2500</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:26:19.306168Z</t>
+          <t>2026-08-02T16:18:13.528514Z</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr"/>
@@ -8641,19 +8641,19 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr"/>
       <c r="AA67" s="2" t="inlineStr"/>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.2500</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T03:26:20.027864Z</t>
+          <t>2026-08-02T16:18:13.574073Z</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr"/>
@@ -8885,19 +8885,19 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr"/>
       <c r="AA69" s="2" t="inlineStr"/>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>-1.5000</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02T05:39:25.608387Z</t>
+          <t>2026-08-02T16:18:13.618469Z</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr"/>
@@ -10126,14 +10126,26 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y80" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z80" s="2" t="inlineStr"/>
       <c r="AA80" s="2" t="inlineStr"/>
-      <c r="AB80" s="2" t="inlineStr"/>
-      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1.5600</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:39:25.040147Z</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr"/>
       <c r="AE80" s="2" t="inlineStr"/>
       <c r="AF80" s="2" t="inlineStr"/>
@@ -12012,8 +12024,1492 @@
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>583e9a4fc6e74a5a</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>401841470</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0.3003003003003003</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>0.1558346996996997</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:08.431356Z</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="2" t="inlineStr"/>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="2" t="inlineStr"/>
+      <c r="AJ98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>167e820da4a34ad3</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>0.2298850574712644</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>0.16815394252873558</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:08.536425Z</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr"/>
+      <c r="AE99" s="2" t="inlineStr"/>
+      <c r="AF99" s="2" t="inlineStr"/>
+      <c r="AG99" s="2" t="inlineStr"/>
+      <c r="AH99" s="2" t="inlineStr"/>
+      <c r="AI99" s="2" t="inlineStr"/>
+      <c r="AJ99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>48f204a1e99d42f6</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>0.06643243192488257</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:08.980617Z</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr"/>
+      <c r="AE100" s="2" t="inlineStr"/>
+      <c r="AF100" s="2" t="inlineStr"/>
+      <c r="AG100" s="2" t="inlineStr"/>
+      <c r="AH100" s="2" t="inlineStr"/>
+      <c r="AI100" s="2" t="inlineStr"/>
+      <c r="AJ100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>000dce9114bf4b73</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>401844015</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:09.690642Z</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr"/>
+      <c r="AE101" s="2" t="inlineStr"/>
+      <c r="AF101" s="2" t="inlineStr"/>
+      <c r="AG101" s="2" t="inlineStr"/>
+      <c r="AH101" s="2" t="inlineStr"/>
+      <c r="AI101" s="2" t="inlineStr"/>
+      <c r="AJ101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>96c982948bf7445b</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>0.09642276978417269</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:10.319650Z</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr"/>
+      <c r="AE102" s="2" t="inlineStr"/>
+      <c r="AF102" s="2" t="inlineStr"/>
+      <c r="AG102" s="2" t="inlineStr"/>
+      <c r="AH102" s="2" t="inlineStr"/>
+      <c r="AI102" s="2" t="inlineStr"/>
+      <c r="AJ102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>1b4b60e460fa46e4</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr"/>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:10.262963Z</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr"/>
+      <c r="AE103" s="2" t="inlineStr"/>
+      <c r="AF103" s="2" t="inlineStr"/>
+      <c r="AG103" s="2" t="inlineStr"/>
+      <c r="AH103" s="2" t="inlineStr"/>
+      <c r="AI103" s="2" t="inlineStr"/>
+      <c r="AJ103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>644b1da89a89409f</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>-0.06309576923076915</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:10.820622Z</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
+      <c r="AE104" s="2" t="inlineStr"/>
+      <c r="AF104" s="2" t="inlineStr"/>
+      <c r="AG104" s="2" t="inlineStr"/>
+      <c r="AH104" s="2" t="inlineStr"/>
+      <c r="AI104" s="2" t="inlineStr"/>
+      <c r="AJ104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>192020996f9c4bed</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr"/>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:11.344005Z</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr"/>
+      <c r="AE105" s="2" t="inlineStr"/>
+      <c r="AF105" s="2" t="inlineStr"/>
+      <c r="AG105" s="2" t="inlineStr"/>
+      <c r="AH105" s="2" t="inlineStr"/>
+      <c r="AI105" s="2" t="inlineStr"/>
+      <c r="AJ105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>7d88abede7ad40c8</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:11.996978Z</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr"/>
+      <c r="AE106" s="2" t="inlineStr"/>
+      <c r="AF106" s="2" t="inlineStr"/>
+      <c r="AG106" s="2" t="inlineStr"/>
+      <c r="AH106" s="2" t="inlineStr"/>
+      <c r="AI106" s="2" t="inlineStr"/>
+      <c r="AJ106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>043c63f293f44938</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr"/>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>0.14529099999999995</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:13.051822Z</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr"/>
+      <c r="AB107" s="2" t="inlineStr"/>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr"/>
+      <c r="AE107" s="2" t="inlineStr"/>
+      <c r="AF107" s="2" t="inlineStr"/>
+      <c r="AG107" s="2" t="inlineStr"/>
+      <c r="AH107" s="2" t="inlineStr"/>
+      <c r="AI107" s="2" t="inlineStr"/>
+      <c r="AJ107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>6eeb804262304e34</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:13.076403Z</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr"/>
+      <c r="AE108" s="2" t="inlineStr"/>
+      <c r="AF108" s="2" t="inlineStr"/>
+      <c r="AG108" s="2" t="inlineStr"/>
+      <c r="AH108" s="2" t="inlineStr"/>
+      <c r="AI108" s="2" t="inlineStr"/>
+      <c r="AJ108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>d36dcd69eb354ad8</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr"/>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:14.638862Z</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr"/>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
+      <c r="AB109" s="2" t="inlineStr"/>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr"/>
+      <c r="AE109" s="2" t="inlineStr"/>
+      <c r="AF109" s="2" t="inlineStr"/>
+      <c r="AG109" s="2" t="inlineStr"/>
+      <c r="AH109" s="2" t="inlineStr"/>
+      <c r="AI109" s="2" t="inlineStr"/>
+      <c r="AJ109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ccf8d927d6e24108</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>0.06654094557823131</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:15.198916Z</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr"/>
+      <c r="AB110" s="2" t="inlineStr"/>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr"/>
+      <c r="AE110" s="2" t="inlineStr"/>
+      <c r="AF110" s="2" t="inlineStr"/>
+      <c r="AG110" s="2" t="inlineStr"/>
+      <c r="AH110" s="2" t="inlineStr"/>
+      <c r="AI110" s="2" t="inlineStr"/>
+      <c r="AJ110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>336b354a059549d3</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr"/>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>-0.0968399327731092</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:10:17.255205Z</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr"/>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
+      <c r="AB111" s="2" t="inlineStr"/>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr"/>
+      <c r="AE111" s="2" t="inlineStr"/>
+      <c r="AF111" s="2" t="inlineStr"/>
+      <c r="AG111" s="2" t="inlineStr"/>
+      <c r="AH111" s="2" t="inlineStr"/>
+      <c r="AI111" s="2" t="inlineStr"/>
+      <c r="AJ111" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ97"/>
+  <autoFilter ref="A1:AJ111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ111"/>
+  <dimension ref="A1:AJ139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -13508,8 +13508,2976 @@
       <c r="AI111" s="2" t="inlineStr"/>
       <c r="AJ111" s="2" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>9151cb51419a476a</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>401841470</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0.3003003003003003</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>0.1558346996996997</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:47.922820Z</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr"/>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
+      <c r="AB112" s="2" t="inlineStr"/>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr"/>
+      <c r="AE112" s="2" t="inlineStr"/>
+      <c r="AF112" s="2" t="inlineStr"/>
+      <c r="AG112" s="2" t="inlineStr"/>
+      <c r="AH112" s="2" t="inlineStr"/>
+      <c r="AI112" s="2" t="inlineStr"/>
+      <c r="AJ112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>544e1f8d577f4be7</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>0.2298850574712644</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>0.16815394252873558</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:47.966108Z</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
+      <c r="AB113" s="2" t="inlineStr"/>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr"/>
+      <c r="AE113" s="2" t="inlineStr"/>
+      <c r="AF113" s="2" t="inlineStr"/>
+      <c r="AG113" s="2" t="inlineStr"/>
+      <c r="AH113" s="2" t="inlineStr"/>
+      <c r="AI113" s="2" t="inlineStr"/>
+      <c r="AJ113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>563f429118e244a4</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0.06643243192488257</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:48.493240Z</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
+      <c r="AB114" s="2" t="inlineStr"/>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr"/>
+      <c r="AE114" s="2" t="inlineStr"/>
+      <c r="AF114" s="2" t="inlineStr"/>
+      <c r="AG114" s="2" t="inlineStr"/>
+      <c r="AH114" s="2" t="inlineStr"/>
+      <c r="AI114" s="2" t="inlineStr"/>
+      <c r="AJ114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>1cacb0d212ee4808</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>401844015</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:49.122403Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr"/>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>cb2e99d6fc6f4ec9</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>0.09642276978417269</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:49.708693Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>95a8732caa8c48a6</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:49.665497Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr"/>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>f0cdd5c40cc04e47</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>-0.06309576923076915</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:50.252856Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr"/>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>4671c60d9ab84112</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:50.791791Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>01628725ac4843e0</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:51.479072Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr"/>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>267deadf5d91456a</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.14529099999999995</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:52.604138Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr"/>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>09705c3a0e514c0a</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:52.587598Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>f46e46931532468a</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:54.368930Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>b5d275667ffd423d</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0.06654094557823131</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:54.916251Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr"/>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>c11ace7ea16f4f53</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>-0.0968399327731092</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:40:56.660642Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr"/>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>bf22586f70314809</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>401841470</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.3003003003003003</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.1558346996996997</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:34.772770Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr"/>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>06792179234647a7</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:34.761524Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr"/>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>35af8ba9bd154d0a</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.06643243192488257</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:35.319407Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>8ef5bbf3452d4d3e</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>401844015</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:35.929520Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>90d4a6a1650a4db8</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0.09642276978417269</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:36.485049Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>888740c20a784162</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:36.452468Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>33c7ccfe64a24a2b</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>-0.06309576923076915</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:36.997419Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>c5b50f16be8f4bbe</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:37.549387Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ad14d0cf8be14726</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:38.138409Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2e568020fb0e4de6</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0.14529099999999995</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:39.241482Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>9a23432a07ad4cf2</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:39.244934Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>39775ba1c19c4641</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:40.806031Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>791bc0a91ed84544</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.06654094557823131</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:41.338397Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ee4eb806c7624ab3</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>-0.0968399327731092</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:43.017604Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ111"/>
+  <autoFilter ref="A1:AJ139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -9906,14 +9906,26 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y78" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z78" s="2" t="inlineStr"/>
       <c r="AA78" s="2" t="inlineStr"/>
-      <c r="AB78" s="2" t="inlineStr"/>
-      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0.7874</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:15:07.764713Z</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr"/>
       <c r="AE78" s="2" t="inlineStr"/>
       <c r="AF78" s="2" t="inlineStr"/>

--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ139"/>
+  <dimension ref="A1:AJ152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -16488,8 +16488,1386 @@
       <c r="AI139" s="2" t="inlineStr"/>
       <c r="AJ139" s="2" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>fe38e3c546714c7d</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:15.030273Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>a219417ef6bc4b3e</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.03591599999999995</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:15.551432Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>0469a81542cd4b15</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>401844015</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:16.180196Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>0fbbb5da49344695</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>401844019</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>0.09642276978417269</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:16.767102Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>24453b24ca6c4d68</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:16.791251Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>28b23fe9fd2b4403</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>-0.06309576923076915</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:17.306439Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>b7affddf00fb4bab</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:17.804212Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>f6dc2cc5bab04992</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:18.393750Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>73639c6090eb4b5d</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.12607993442622945</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:19.493436Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>5355800012ff4e64</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:19.505283Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>9dc707e7f6ce42f9</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:21.132932Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>7644d7327e044e99</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:21.600849Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>4ca6e28cb0034019</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>-0.12638300000000002</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:23.218067Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ139"/>
+  <autoFilter ref="A1:AJ152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ152"/>
+  <dimension ref="A1:AJ174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17866,8 +17866,2340 @@
       <c r="AI152" s="2" t="inlineStr"/>
       <c r="AJ152" s="2" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>d6b583ae5ba6458a</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:03:57.085051Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>61e687384a564f54</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.03591599999999995</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:03:57.446376Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>014ea93d56dd4903</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:03:58.590991Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>d76178fe036d4807</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>-0.07438143192488261</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:03:59.060066Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>e0f926d658c84ebb</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:03:59.584256Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>6675df53a75c4df0</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:00.177862Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>39df0ddf95fe47ff</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>0.12607993442622945</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:01.212035Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>5466045ebae747ac</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:01.215935Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>878b49d8cfed49f8</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:02.208746Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>975aa21441f14634</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:02.666215Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>fa2dfd77ff444361</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>-0.13677986311787071</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:04.179302Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>3bf1d059beab4a8d</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:50.915614Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>3b033ea31a334fd1</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>0.03591599999999995</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:51.454474Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>d6c7e08773d54c8b</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:52.585276Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>0749449e306f4b48</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>-0.07438143192488261</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:53.154543Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>4d4d63f5d8144679</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>0.05613499999999999</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:53.698692Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>a55e7e2b3fde459e</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:54.348066Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>9db16f4461f546fa</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.12607993442622945</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:55.430903Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2a071dace8a744c0</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:55.431198Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>030a64f94add474c</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:56.584323Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>bb9e9965eee64d89</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:57.084113Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>32e7beb5481e40da</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>-0.13677986311787071</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:07:58.632384Z</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
+      <c r="AG174" s="2" t="inlineStr"/>
+      <c r="AH174" s="2" t="inlineStr"/>
+      <c r="AI174" s="2" t="inlineStr"/>
+      <c r="AJ174" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ152"/>
+  <autoFilter ref="A1:AJ174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ174"/>
+  <dimension ref="A1:AJ185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11910,14 +11910,26 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y96" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z96" s="2" t="inlineStr"/>
       <c r="AA96" s="2" t="inlineStr"/>
-      <c r="AB96" s="2" t="inlineStr"/>
-      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1.4423</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:18:44.875325Z</t>
+        </is>
+      </c>
       <c r="AD96" s="2" t="inlineStr"/>
       <c r="AE96" s="2" t="inlineStr"/>
       <c r="AF96" s="2" t="inlineStr"/>
@@ -20198,8 +20210,1174 @@
       <c r="AI174" s="2" t="inlineStr"/>
       <c r="AJ174" s="2" t="inlineStr"/>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>6d80c1ab928140e0</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:57.657891Z</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
+      <c r="AG175" s="2" t="inlineStr"/>
+      <c r="AH175" s="2" t="inlineStr"/>
+      <c r="AI175" s="2" t="inlineStr"/>
+      <c r="AJ175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2b777dd1161a45c5</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>0.026112078431372532</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:58.152453Z</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
+      <c r="AG176" s="2" t="inlineStr"/>
+      <c r="AH176" s="2" t="inlineStr"/>
+      <c r="AI176" s="2" t="inlineStr"/>
+      <c r="AJ176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>c632aecc54254724</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>401844012</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:59.331517Z</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
+      <c r="AG177" s="2" t="inlineStr"/>
+      <c r="AH177" s="2" t="inlineStr"/>
+      <c r="AI177" s="2" t="inlineStr"/>
+      <c r="AJ177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2f9591b24f804e3f</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>-0.07438143192488261</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:59.851446Z</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
+      <c r="AG178" s="2" t="inlineStr"/>
+      <c r="AH178" s="2" t="inlineStr"/>
+      <c r="AI178" s="2" t="inlineStr"/>
+      <c r="AJ178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>583a23176fb54834</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.04629893442622951</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:00.330798Z</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
+      <c r="AG179" s="2" t="inlineStr"/>
+      <c r="AH179" s="2" t="inlineStr"/>
+      <c r="AI179" s="2" t="inlineStr"/>
+      <c r="AJ179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>8631dccbcbe242de</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:01.037022Z</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
+      <c r="AG180" s="2" t="inlineStr"/>
+      <c r="AH180" s="2" t="inlineStr"/>
+      <c r="AI180" s="2" t="inlineStr"/>
+      <c r="AJ180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>0b594c42ac6f4946</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0.12607993442622945</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:02.097668Z</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+      <c r="AB181" s="2" t="inlineStr"/>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr"/>
+      <c r="AE181" s="2" t="inlineStr"/>
+      <c r="AF181" s="2" t="inlineStr"/>
+      <c r="AG181" s="2" t="inlineStr"/>
+      <c r="AH181" s="2" t="inlineStr"/>
+      <c r="AI181" s="2" t="inlineStr"/>
+      <c r="AJ181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>90b74cfa4eeb448b</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:02.121236Z</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+      <c r="AB182" s="2" t="inlineStr"/>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr"/>
+      <c r="AE182" s="2" t="inlineStr"/>
+      <c r="AF182" s="2" t="inlineStr"/>
+      <c r="AG182" s="2" t="inlineStr"/>
+      <c r="AH182" s="2" t="inlineStr"/>
+      <c r="AI182" s="2" t="inlineStr"/>
+      <c r="AJ182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>b0eba40b32d74a59</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr"/>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:03.178265Z</t>
+        </is>
+      </c>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+      <c r="AB183" s="2" t="inlineStr"/>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr"/>
+      <c r="AE183" s="2" t="inlineStr"/>
+      <c r="AF183" s="2" t="inlineStr"/>
+      <c r="AG183" s="2" t="inlineStr"/>
+      <c r="AH183" s="2" t="inlineStr"/>
+      <c r="AI183" s="2" t="inlineStr"/>
+      <c r="AJ183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>7f5c52cfb2244616</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:03.706476Z</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+      <c r="AB184" s="2" t="inlineStr"/>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr"/>
+      <c r="AE184" s="2" t="inlineStr"/>
+      <c r="AF184" s="2" t="inlineStr"/>
+      <c r="AG184" s="2" t="inlineStr"/>
+      <c r="AH184" s="2" t="inlineStr"/>
+      <c r="AI184" s="2" t="inlineStr"/>
+      <c r="AJ184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>9fa4e33e0c174e4a</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>-0.13677986311787071</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:05.281009Z</t>
+        </is>
+      </c>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+      <c r="AB185" s="2" t="inlineStr"/>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr"/>
+      <c r="AE185" s="2" t="inlineStr"/>
+      <c r="AF185" s="2" t="inlineStr"/>
+      <c r="AG185" s="2" t="inlineStr"/>
+      <c r="AH185" s="2" t="inlineStr"/>
+      <c r="AI185" s="2" t="inlineStr"/>
+      <c r="AJ185" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ174"/>
+  <autoFilter ref="A1:AJ185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ185"/>
+  <dimension ref="A1:AJ210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -16802,14 +16802,26 @@
       <c r="W142" s="2" t="inlineStr"/>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y142" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z142" s="2" t="inlineStr"/>
       <c r="AA142" s="2" t="inlineStr"/>
-      <c r="AB142" s="2" t="inlineStr"/>
-      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr">
+        <is>
+          <t>1.2200</t>
+        </is>
+      </c>
+      <c r="AC142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:19.120421Z</t>
+        </is>
+      </c>
       <c r="AD142" s="2" t="inlineStr"/>
       <c r="AE142" s="2" t="inlineStr"/>
       <c r="AF142" s="2" t="inlineStr"/>
@@ -16908,14 +16920,26 @@
       <c r="W143" s="2" t="inlineStr"/>
       <c r="X143" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y143" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z143" s="2" t="inlineStr"/>
       <c r="AA143" s="2" t="inlineStr"/>
-      <c r="AB143" s="2" t="inlineStr"/>
-      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr">
+        <is>
+          <t>1.7800</t>
+        </is>
+      </c>
+      <c r="AC143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:11:46.472031Z</t>
+        </is>
+      </c>
       <c r="AD143" s="2" t="inlineStr"/>
       <c r="AE143" s="2" t="inlineStr"/>
       <c r="AF143" s="2" t="inlineStr"/>
@@ -20512,14 +20536,26 @@
       <c r="W177" s="2" t="inlineStr"/>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y177" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z177" s="2" t="inlineStr"/>
       <c r="AA177" s="2" t="inlineStr"/>
-      <c r="AB177" s="2" t="inlineStr"/>
-      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:28.173623Z</t>
+        </is>
+      </c>
       <c r="AD177" s="2" t="inlineStr"/>
       <c r="AE177" s="2" t="inlineStr"/>
       <c r="AF177" s="2" t="inlineStr"/>
@@ -21376,8 +21412,2778 @@
       <c r="AI185" s="2" t="inlineStr"/>
       <c r="AJ185" s="2" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>8a18629f7b214ef4</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>0.21978021978021978</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>0.1782587802197802</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:50.950228Z</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+      <c r="AB186" s="2" t="inlineStr"/>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr"/>
+      <c r="AE186" s="2" t="inlineStr"/>
+      <c r="AF186" s="2" t="inlineStr"/>
+      <c r="AG186" s="2" t="inlineStr"/>
+      <c r="AH186" s="2" t="inlineStr"/>
+      <c r="AI186" s="2" t="inlineStr"/>
+      <c r="AJ186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>7afb430e8cb644d6</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr"/>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>0.026112078431372532</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:51.380327Z</t>
+        </is>
+      </c>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+      <c r="AB187" s="2" t="inlineStr"/>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr"/>
+      <c r="AE187" s="2" t="inlineStr"/>
+      <c r="AF187" s="2" t="inlineStr"/>
+      <c r="AG187" s="2" t="inlineStr"/>
+      <c r="AH187" s="2" t="inlineStr"/>
+      <c r="AI187" s="2" t="inlineStr"/>
+      <c r="AJ187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>744973ff99614f3d</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>401844026</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>-0.07438143192488261</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:53.116696Z</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+      <c r="AB188" s="2" t="inlineStr">
+        <is>
+          <t>0.8850</t>
+        </is>
+      </c>
+      <c r="AC188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:36.122850Z</t>
+        </is>
+      </c>
+      <c r="AD188" s="2" t="inlineStr"/>
+      <c r="AE188" s="2" t="inlineStr"/>
+      <c r="AF188" s="2" t="inlineStr"/>
+      <c r="AG188" s="2" t="inlineStr"/>
+      <c r="AH188" s="2" t="inlineStr"/>
+      <c r="AI188" s="2" t="inlineStr"/>
+      <c r="AJ188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>faa0b3369f2148e8</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr"/>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>0.04629893442622951</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:53.636385Z</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+      <c r="AB189" s="2" t="inlineStr"/>
+      <c r="AC189" s="2" t="inlineStr"/>
+      <c r="AD189" s="2" t="inlineStr"/>
+      <c r="AE189" s="2" t="inlineStr"/>
+      <c r="AF189" s="2" t="inlineStr"/>
+      <c r="AG189" s="2" t="inlineStr"/>
+      <c r="AH189" s="2" t="inlineStr"/>
+      <c r="AI189" s="2" t="inlineStr"/>
+      <c r="AJ189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>3f1197c7b0d44717</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr"/>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:54.256107Z</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+      <c r="AB190" s="2" t="inlineStr"/>
+      <c r="AC190" s="2" t="inlineStr"/>
+      <c r="AD190" s="2" t="inlineStr"/>
+      <c r="AE190" s="2" t="inlineStr"/>
+      <c r="AF190" s="2" t="inlineStr"/>
+      <c r="AG190" s="2" t="inlineStr"/>
+      <c r="AH190" s="2" t="inlineStr"/>
+      <c r="AI190" s="2" t="inlineStr"/>
+      <c r="AJ190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>ef3c95a441a14131</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>401850609</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr"/>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>0.12607993442622945</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:55.406216Z</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:00Z</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+      <c r="AB191" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:11:53.211060Z</t>
+        </is>
+      </c>
+      <c r="AD191" s="2" t="inlineStr"/>
+      <c r="AE191" s="2" t="inlineStr"/>
+      <c r="AF191" s="2" t="inlineStr"/>
+      <c r="AG191" s="2" t="inlineStr"/>
+      <c r="AH191" s="2" t="inlineStr"/>
+      <c r="AI191" s="2" t="inlineStr"/>
+      <c r="AJ191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ddd11cdc98814c6c</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr"/>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:55.391698Z</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
+      <c r="AB192" s="2" t="inlineStr"/>
+      <c r="AC192" s="2" t="inlineStr"/>
+      <c r="AD192" s="2" t="inlineStr"/>
+      <c r="AE192" s="2" t="inlineStr"/>
+      <c r="AF192" s="2" t="inlineStr"/>
+      <c r="AG192" s="2" t="inlineStr"/>
+      <c r="AH192" s="2" t="inlineStr"/>
+      <c r="AI192" s="2" t="inlineStr"/>
+      <c r="AJ192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>1495495ccd854be3</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr"/>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>-0.21383199669966996</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:56.540469Z</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr"/>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
+      <c r="AB193" s="2" t="inlineStr"/>
+      <c r="AC193" s="2" t="inlineStr"/>
+      <c r="AD193" s="2" t="inlineStr"/>
+      <c r="AE193" s="2" t="inlineStr"/>
+      <c r="AF193" s="2" t="inlineStr"/>
+      <c r="AG193" s="2" t="inlineStr"/>
+      <c r="AH193" s="2" t="inlineStr"/>
+      <c r="AI193" s="2" t="inlineStr"/>
+      <c r="AJ193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>6a71882e14d74453</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr"/>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:57.045848Z</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr"/>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
+      <c r="AB194" s="2" t="inlineStr"/>
+      <c r="AC194" s="2" t="inlineStr"/>
+      <c r="AD194" s="2" t="inlineStr"/>
+      <c r="AE194" s="2" t="inlineStr"/>
+      <c r="AF194" s="2" t="inlineStr"/>
+      <c r="AG194" s="2" t="inlineStr"/>
+      <c r="AH194" s="2" t="inlineStr"/>
+      <c r="AI194" s="2" t="inlineStr"/>
+      <c r="AJ194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>3cd63ae7cd604ee2</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr"/>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>-0.13677986311787071</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:44:58.687658Z</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr"/>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
+      <c r="AB195" s="2" t="inlineStr"/>
+      <c r="AC195" s="2" t="inlineStr"/>
+      <c r="AD195" s="2" t="inlineStr"/>
+      <c r="AE195" s="2" t="inlineStr"/>
+      <c r="AF195" s="2" t="inlineStr"/>
+      <c r="AG195" s="2" t="inlineStr"/>
+      <c r="AH195" s="2" t="inlineStr"/>
+      <c r="AI195" s="2" t="inlineStr"/>
+      <c r="AJ195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ac8b11d7f85e4484</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>401841473</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>0.398039</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr"/>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>0.19803899999999997</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:41.940716Z</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+      <c r="AB196" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:11:55.657413Z</t>
+        </is>
+      </c>
+      <c r="AD196" s="2" t="inlineStr"/>
+      <c r="AE196" s="2" t="inlineStr"/>
+      <c r="AF196" s="2" t="inlineStr"/>
+      <c r="AG196" s="2" t="inlineStr"/>
+      <c r="AH196" s="2" t="inlineStr"/>
+      <c r="AI196" s="2" t="inlineStr"/>
+      <c r="AJ196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>d7552edce8a64f15</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>401841476</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>0.535916</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr"/>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>0.016685230769230786</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:42.008763Z</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:15Z</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr"/>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
+      <c r="AB197" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:22.468068Z</t>
+        </is>
+      </c>
+      <c r="AD197" s="2" t="inlineStr"/>
+      <c r="AE197" s="2" t="inlineStr"/>
+      <c r="AF197" s="2" t="inlineStr"/>
+      <c r="AG197" s="2" t="inlineStr"/>
+      <c r="AH197" s="2" t="inlineStr"/>
+      <c r="AI197" s="2" t="inlineStr"/>
+      <c r="AJ197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>085941b91b6d4d37</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>401844014</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr"/>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>0.04629893442622951</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:44.125260Z</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr"/>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
+      <c r="AB198" s="2" t="inlineStr">
+        <is>
+          <t>1.4400</t>
+        </is>
+      </c>
+      <c r="AC198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:52.127811Z</t>
+        </is>
+      </c>
+      <c r="AD198" s="2" t="inlineStr"/>
+      <c r="AE198" s="2" t="inlineStr"/>
+      <c r="AF198" s="2" t="inlineStr"/>
+      <c r="AG198" s="2" t="inlineStr"/>
+      <c r="AH198" s="2" t="inlineStr"/>
+      <c r="AI198" s="2" t="inlineStr"/>
+      <c r="AJ198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>84e206a9748e4007</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>0.4608294930875576</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr"/>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>-0.004694493087557594</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:44.997804Z</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr"/>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
+      <c r="AB199" s="2" t="inlineStr"/>
+      <c r="AC199" s="2" t="inlineStr"/>
+      <c r="AD199" s="2" t="inlineStr"/>
+      <c r="AE199" s="2" t="inlineStr"/>
+      <c r="AF199" s="2" t="inlineStr"/>
+      <c r="AG199" s="2" t="inlineStr"/>
+      <c r="AH199" s="2" t="inlineStr"/>
+      <c r="AI199" s="2" t="inlineStr"/>
+      <c r="AJ199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>9020f970735c4ad9</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>401850607</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>0.414794</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr"/>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>-0.22549376978417268</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:46.129780Z</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+      <c r="AB200" s="2" t="inlineStr">
+        <is>
+          <t>0.5618</t>
+        </is>
+      </c>
+      <c r="AC200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:24.829693Z</t>
+        </is>
+      </c>
+      <c r="AD200" s="2" t="inlineStr"/>
+      <c r="AE200" s="2" t="inlineStr"/>
+      <c r="AF200" s="2" t="inlineStr"/>
+      <c r="AG200" s="2" t="inlineStr"/>
+      <c r="AH200" s="2" t="inlineStr"/>
+      <c r="AI200" s="2" t="inlineStr"/>
+      <c r="AJ200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>6858c1b49d6941bd</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>401859644</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr"/>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>-0.20372894557823135</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:47.244780Z</t>
+        </is>
+      </c>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:30Z</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+      <c r="AB201" s="2" t="inlineStr">
+        <is>
+          <t>0.5155</t>
+        </is>
+      </c>
+      <c r="AC201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:54.558753Z</t>
+        </is>
+      </c>
+      <c r="AD201" s="2" t="inlineStr"/>
+      <c r="AE201" s="2" t="inlineStr"/>
+      <c r="AF201" s="2" t="inlineStr"/>
+      <c r="AG201" s="2" t="inlineStr"/>
+      <c r="AH201" s="2" t="inlineStr"/>
+      <c r="AI201" s="2" t="inlineStr"/>
+      <c r="AJ201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>65fc2e69dfbd4206</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>401859718</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>0.406677</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr"/>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>0.07664399669966998</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:47.766469Z</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:10Z</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+      <c r="AB202" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:34:06.326733Z</t>
+        </is>
+      </c>
+      <c r="AD202" s="2" t="inlineStr"/>
+      <c r="AE202" s="2" t="inlineStr"/>
+      <c r="AF202" s="2" t="inlineStr"/>
+      <c r="AG202" s="2" t="inlineStr"/>
+      <c r="AH202" s="2" t="inlineStr"/>
+      <c r="AI202" s="2" t="inlineStr"/>
+      <c r="AJ202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>a788ae35a1bd4027</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>401863533</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>0.482992</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr"/>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>-0.017008000000000023</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:27:49.278173Z</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+      <c r="AB203" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:12:57.215509Z</t>
+        </is>
+      </c>
+      <c r="AD203" s="2" t="inlineStr"/>
+      <c r="AE203" s="2" t="inlineStr"/>
+      <c r="AF203" s="2" t="inlineStr"/>
+      <c r="AG203" s="2" t="inlineStr"/>
+      <c r="AH203" s="2" t="inlineStr"/>
+      <c r="AI203" s="2" t="inlineStr"/>
+      <c r="AJ203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2fb013280d794c63</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>401877966</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>0.4504504504504505</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr"/>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>0.0056845495495495</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:14:00.014557Z</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T01:00Z</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+      <c r="AB204" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:11:00.983998Z</t>
+        </is>
+      </c>
+      <c r="AD204" s="2" t="inlineStr"/>
+      <c r="AE204" s="2" t="inlineStr"/>
+      <c r="AF204" s="2" t="inlineStr"/>
+      <c r="AG204" s="2" t="inlineStr"/>
+      <c r="AH204" s="2" t="inlineStr"/>
+      <c r="AI204" s="2" t="inlineStr"/>
+      <c r="AJ204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>b1329db6f20f41a2</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr"/>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr"/>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:12:04.126670Z</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr"/>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+      <c r="AB205" s="2" t="inlineStr"/>
+      <c r="AC205" s="2" t="inlineStr"/>
+      <c r="AD205" s="2" t="inlineStr"/>
+      <c r="AE205" s="2" t="inlineStr"/>
+      <c r="AF205" s="2" t="inlineStr"/>
+      <c r="AG205" s="2" t="inlineStr"/>
+      <c r="AH205" s="2" t="inlineStr"/>
+      <c r="AI205" s="2" t="inlineStr"/>
+      <c r="AJ205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>0729102029b345fa</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr"/>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr"/>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:23:59.708892Z</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr"/>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+      <c r="AB206" s="2" t="inlineStr"/>
+      <c r="AC206" s="2" t="inlineStr"/>
+      <c r="AD206" s="2" t="inlineStr"/>
+      <c r="AE206" s="2" t="inlineStr"/>
+      <c r="AF206" s="2" t="inlineStr"/>
+      <c r="AG206" s="2" t="inlineStr"/>
+      <c r="AH206" s="2" t="inlineStr"/>
+      <c r="AI206" s="2" t="inlineStr"/>
+      <c r="AJ206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>282cf0d205364e4d</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr"/>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr"/>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:07:42.147500Z</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr"/>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+      <c r="AB207" s="2" t="inlineStr"/>
+      <c r="AC207" s="2" t="inlineStr"/>
+      <c r="AD207" s="2" t="inlineStr"/>
+      <c r="AE207" s="2" t="inlineStr"/>
+      <c r="AF207" s="2" t="inlineStr"/>
+      <c r="AG207" s="2" t="inlineStr"/>
+      <c r="AH207" s="2" t="inlineStr"/>
+      <c r="AI207" s="2" t="inlineStr"/>
+      <c r="AJ207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>664938e28afc4407</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr"/>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr"/>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:46:08.643914Z</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr"/>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr"/>
+      <c r="AB208" s="2" t="inlineStr"/>
+      <c r="AC208" s="2" t="inlineStr"/>
+      <c r="AD208" s="2" t="inlineStr"/>
+      <c r="AE208" s="2" t="inlineStr"/>
+      <c r="AF208" s="2" t="inlineStr"/>
+      <c r="AG208" s="2" t="inlineStr"/>
+      <c r="AH208" s="2" t="inlineStr"/>
+      <c r="AI208" s="2" t="inlineStr"/>
+      <c r="AJ208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>eddb15954a3c49bf</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr"/>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr"/>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:56:34.514036Z</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr"/>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
+      <c r="AB209" s="2" t="inlineStr"/>
+      <c r="AC209" s="2" t="inlineStr"/>
+      <c r="AD209" s="2" t="inlineStr"/>
+      <c r="AE209" s="2" t="inlineStr"/>
+      <c r="AF209" s="2" t="inlineStr"/>
+      <c r="AG209" s="2" t="inlineStr"/>
+      <c r="AH209" s="2" t="inlineStr"/>
+      <c r="AI209" s="2" t="inlineStr"/>
+      <c r="AJ209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>30b1fee74bca4b62</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>34d1568aad0ff11b5db35f118324684f93281e1c21fa7b80be7a4a4e2cb4bb03</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>401872729</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>0.473701</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr"/>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr"/>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>-0.1061309327731092</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:27:54.429463Z</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T22:00Z</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr"/>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr"/>
+      <c r="AB210" s="2" t="inlineStr"/>
+      <c r="AC210" s="2" t="inlineStr"/>
+      <c r="AD210" s="2" t="inlineStr"/>
+      <c r="AE210" s="2" t="inlineStr"/>
+      <c r="AF210" s="2" t="inlineStr"/>
+      <c r="AG210" s="2" t="inlineStr"/>
+      <c r="AH210" s="2" t="inlineStr"/>
+      <c r="AI210" s="2" t="inlineStr"/>
+      <c r="AJ210" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ185"/>
+  <autoFilter ref="A1:AJ210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ210"/>
+  <dimension ref="A1:AJ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -24182,8 +24182,754 @@
       <c r="AI210" s="2" t="inlineStr"/>
       <c r="AJ210" s="2" t="inlineStr"/>
     </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>d615caecc5f94d7b</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>401902573</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr"/>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>0.2102019455782313</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:31.711259Z</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr"/>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+      <c r="AB211" s="2" t="inlineStr"/>
+      <c r="AC211" s="2" t="inlineStr"/>
+      <c r="AD211" s="2" t="inlineStr"/>
+      <c r="AE211" s="2" t="inlineStr"/>
+      <c r="AF211" s="2" t="inlineStr"/>
+      <c r="AG211" s="2" t="inlineStr"/>
+      <c r="AH211" s="2" t="inlineStr"/>
+      <c r="AI211" s="2" t="inlineStr"/>
+      <c r="AJ211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>f6d2b1bdd73f4394</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>401902573</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr"/>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>-0.07438143192488261</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:31.490640Z</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr"/>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+      <c r="AB212" s="2" t="inlineStr"/>
+      <c r="AC212" s="2" t="inlineStr"/>
+      <c r="AD212" s="2" t="inlineStr"/>
+      <c r="AE212" s="2" t="inlineStr"/>
+      <c r="AF212" s="2" t="inlineStr"/>
+      <c r="AG212" s="2" t="inlineStr"/>
+      <c r="AH212" s="2" t="inlineStr"/>
+      <c r="AI212" s="2" t="inlineStr"/>
+      <c r="AJ212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>cd845535e9fc4c2d</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>401886555</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>0.417429</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr"/>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr"/>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>-0.23292065034965032</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:32.473435Z</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:30Z</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+      <c r="AB213" s="2" t="inlineStr"/>
+      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AD213" s="2" t="inlineStr"/>
+      <c r="AE213" s="2" t="inlineStr"/>
+      <c r="AF213" s="2" t="inlineStr"/>
+      <c r="AG213" s="2" t="inlineStr"/>
+      <c r="AH213" s="2" t="inlineStr"/>
+      <c r="AI213" s="2" t="inlineStr"/>
+      <c r="AJ213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>a210d629466642e9</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>401867394</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>0.530727</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr"/>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr"/>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>0.00021056807511732334</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:32.336635Z</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:30Z</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr"/>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+      <c r="AB214" s="2" t="inlineStr"/>
+      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AD214" s="2" t="inlineStr"/>
+      <c r="AE214" s="2" t="inlineStr"/>
+      <c r="AF214" s="2" t="inlineStr"/>
+      <c r="AG214" s="2" t="inlineStr"/>
+      <c r="AH214" s="2" t="inlineStr"/>
+      <c r="AI214" s="2" t="inlineStr"/>
+      <c r="AJ214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>237cd34ac3464ad4</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>401906432</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>0.465639</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr"/>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr"/>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>0.05580293442622952</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:32.663481Z</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:45Z</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr"/>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
+      <c r="AB215" s="2" t="inlineStr"/>
+      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AD215" s="2" t="inlineStr"/>
+      <c r="AE215" s="2" t="inlineStr"/>
+      <c r="AF215" s="2" t="inlineStr"/>
+      <c r="AG215" s="2" t="inlineStr"/>
+      <c r="AH215" s="2" t="inlineStr"/>
+      <c r="AI215" s="2" t="inlineStr"/>
+      <c r="AJ215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>b253deda3d5d4912</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>401887955</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>0.444718</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>0.7297297297297298</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr"/>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>-0.2850117297297298</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:32.802271Z</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:00Z</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr"/>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
+      <c r="AB216" s="2" t="inlineStr"/>
+      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AD216" s="2" t="inlineStr"/>
+      <c r="AE216" s="2" t="inlineStr"/>
+      <c r="AF216" s="2" t="inlineStr"/>
+      <c r="AG216" s="2" t="inlineStr"/>
+      <c r="AH216" s="2" t="inlineStr"/>
+      <c r="AI216" s="2" t="inlineStr"/>
+      <c r="AJ216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>aa152124048f4415</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>401906428</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>0.565923</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>0.7198879551820728</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr"/>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>-0.15396495518207287</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:32.874312Z</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:00Z</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr"/>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+      <c r="AB217" s="2" t="inlineStr"/>
+      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AD217" s="2" t="inlineStr"/>
+      <c r="AE217" s="2" t="inlineStr"/>
+      <c r="AF217" s="2" t="inlineStr"/>
+      <c r="AG217" s="2" t="inlineStr"/>
+      <c r="AH217" s="2" t="inlineStr"/>
+      <c r="AI217" s="2" t="inlineStr"/>
+      <c r="AJ217" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ210"/>
+  <autoFilter ref="A1:AJ217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/soccer-poisson-dc.xlsx
+++ b/data/model_ledgers/soccer-poisson-dc.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ217"/>
+  <dimension ref="A1:AJ247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -24488,14 +24488,26 @@
       <c r="W213" s="2" t="inlineStr"/>
       <c r="X213" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y213" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z213" s="2" t="inlineStr"/>
       <c r="AA213" s="2" t="inlineStr"/>
-      <c r="AB213" s="2" t="inlineStr"/>
-      <c r="AC213" s="2" t="inlineStr"/>
+      <c r="AB213" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:20.842266Z</t>
+        </is>
+      </c>
       <c r="AD213" s="2" t="inlineStr"/>
       <c r="AE213" s="2" t="inlineStr"/>
       <c r="AF213" s="2" t="inlineStr"/>
@@ -24594,14 +24606,26 @@
       <c r="W214" s="2" t="inlineStr"/>
       <c r="X214" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y214" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z214" s="2" t="inlineStr"/>
       <c r="AA214" s="2" t="inlineStr"/>
-      <c r="AB214" s="2" t="inlineStr"/>
-      <c r="AC214" s="2" t="inlineStr"/>
+      <c r="AB214" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:21.847490Z</t>
+        </is>
+      </c>
       <c r="AD214" s="2" t="inlineStr"/>
       <c r="AE214" s="2" t="inlineStr"/>
       <c r="AF214" s="2" t="inlineStr"/>
@@ -24700,14 +24724,26 @@
       <c r="W215" s="2" t="inlineStr"/>
       <c r="X215" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y215" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
       <c r="Z215" s="2" t="inlineStr"/>
       <c r="AA215" s="2" t="inlineStr"/>
-      <c r="AB215" s="2" t="inlineStr"/>
-      <c r="AC215" s="2" t="inlineStr"/>
+      <c r="AB215" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:22.847791Z</t>
+        </is>
+      </c>
       <c r="AD215" s="2" t="inlineStr"/>
       <c r="AE215" s="2" t="inlineStr"/>
       <c r="AF215" s="2" t="inlineStr"/>
@@ -24806,14 +24842,26 @@
       <c r="W216" s="2" t="inlineStr"/>
       <c r="X216" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y216" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z216" s="2" t="inlineStr"/>
       <c r="AA216" s="2" t="inlineStr"/>
-      <c r="AB216" s="2" t="inlineStr"/>
-      <c r="AC216" s="2" t="inlineStr"/>
+      <c r="AB216" s="2" t="inlineStr">
+        <is>
+          <t>0.3704</t>
+        </is>
+      </c>
+      <c r="AC216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:14:23.903730Z</t>
+        </is>
+      </c>
       <c r="AD216" s="2" t="inlineStr"/>
       <c r="AE216" s="2" t="inlineStr"/>
       <c r="AF216" s="2" t="inlineStr"/>
@@ -24912,14 +24960,26 @@
       <c r="W217" s="2" t="inlineStr"/>
       <c r="X217" s="2" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="Y217" s="2" t="inlineStr"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
       <c r="Z217" s="2" t="inlineStr"/>
       <c r="AA217" s="2" t="inlineStr"/>
-      <c r="AB217" s="2" t="inlineStr"/>
-      <c r="AC217" s="2" t="inlineStr"/>
+      <c r="AB217" s="2" t="inlineStr">
+        <is>
+          <t>0.3891</t>
+        </is>
+      </c>
+      <c r="AC217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:15.912367Z</t>
+        </is>
+      </c>
       <c r="AD217" s="2" t="inlineStr"/>
       <c r="AE217" s="2" t="inlineStr"/>
       <c r="AF217" s="2" t="inlineStr"/>
@@ -24928,8 +24988,3272 @@
       <c r="AI217" s="2" t="inlineStr"/>
       <c r="AJ217" s="2" t="inlineStr"/>
     </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>5253227a98d84c6a</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>401902573</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr"/>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>0.22030499669966996</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:16:27.752629Z</t>
+        </is>
+      </c>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr"/>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr"/>
+      <c r="AB218" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:45.636190Z</t>
+        </is>
+      </c>
+      <c r="AD218" s="2" t="inlineStr"/>
+      <c r="AE218" s="2" t="inlineStr"/>
+      <c r="AF218" s="2" t="inlineStr"/>
+      <c r="AG218" s="2" t="inlineStr"/>
+      <c r="AH218" s="2" t="inlineStr"/>
+      <c r="AI218" s="2" t="inlineStr"/>
+      <c r="AJ218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>9e35ce634b1e444e</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>401902573</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr"/>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>-0.06309576923076915</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:16:27.579259Z</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr"/>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr"/>
+      <c r="AB219" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:46.603436Z</t>
+        </is>
+      </c>
+      <c r="AD219" s="2" t="inlineStr"/>
+      <c r="AE219" s="2" t="inlineStr"/>
+      <c r="AF219" s="2" t="inlineStr"/>
+      <c r="AG219" s="2" t="inlineStr"/>
+      <c r="AH219" s="2" t="inlineStr"/>
+      <c r="AI219" s="2" t="inlineStr"/>
+      <c r="AJ219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>70eb72d735114178</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>0.0111674930875576</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:35:35.598467Z</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr"/>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
+      <c r="AB220" s="2" t="inlineStr"/>
+      <c r="AC220" s="2" t="inlineStr"/>
+      <c r="AD220" s="2" t="inlineStr"/>
+      <c r="AE220" s="2" t="inlineStr"/>
+      <c r="AF220" s="2" t="inlineStr"/>
+      <c r="AG220" s="2" t="inlineStr"/>
+      <c r="AH220" s="2" t="inlineStr"/>
+      <c r="AI220" s="2" t="inlineStr"/>
+      <c r="AJ220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>91a4abeb4f0640e3</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr"/>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>0.08085443192488262</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:35:35.300678Z</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+      <c r="AB221" s="2" t="inlineStr"/>
+      <c r="AC221" s="2" t="inlineStr"/>
+      <c r="AD221" s="2" t="inlineStr"/>
+      <c r="AE221" s="2" t="inlineStr"/>
+      <c r="AF221" s="2" t="inlineStr"/>
+      <c r="AG221" s="2" t="inlineStr"/>
+      <c r="AH221" s="2" t="inlineStr"/>
+      <c r="AI221" s="2" t="inlineStr"/>
+      <c r="AJ221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>fd60d88f6355486e</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr"/>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>-0.23426747678018572</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:35:35.260673Z</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
+      <c r="AB222" s="2" t="inlineStr"/>
+      <c r="AC222" s="2" t="inlineStr"/>
+      <c r="AD222" s="2" t="inlineStr"/>
+      <c r="AE222" s="2" t="inlineStr"/>
+      <c r="AF222" s="2" t="inlineStr"/>
+      <c r="AG222" s="2" t="inlineStr"/>
+      <c r="AH222" s="2" t="inlineStr"/>
+      <c r="AI222" s="2" t="inlineStr"/>
+      <c r="AJ222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>0e94269388ff4bab</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>-0.12369693277310917</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:35:35.062391Z</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr"/>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr"/>
+      <c r="AB223" s="2" t="inlineStr"/>
+      <c r="AC223" s="2" t="inlineStr"/>
+      <c r="AD223" s="2" t="inlineStr"/>
+      <c r="AE223" s="2" t="inlineStr"/>
+      <c r="AF223" s="2" t="inlineStr"/>
+      <c r="AG223" s="2" t="inlineStr"/>
+      <c r="AH223" s="2" t="inlineStr"/>
+      <c r="AI223" s="2" t="inlineStr"/>
+      <c r="AJ223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>b16afc4d02e34cc9</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr"/>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>-0.08994976978417268</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:05.113909Z</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr"/>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr"/>
+      <c r="AB224" s="2" t="inlineStr"/>
+      <c r="AC224" s="2" t="inlineStr"/>
+      <c r="AD224" s="2" t="inlineStr"/>
+      <c r="AE224" s="2" t="inlineStr"/>
+      <c r="AF224" s="2" t="inlineStr"/>
+      <c r="AG224" s="2" t="inlineStr"/>
+      <c r="AH224" s="2" t="inlineStr"/>
+      <c r="AI224" s="2" t="inlineStr"/>
+      <c r="AJ224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>3798059af2bb42f2</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr"/>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>0.01982156807511737</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:04.862103Z</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr"/>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+      <c r="AB225" s="2" t="inlineStr"/>
+      <c r="AC225" s="2" t="inlineStr"/>
+      <c r="AD225" s="2" t="inlineStr"/>
+      <c r="AE225" s="2" t="inlineStr"/>
+      <c r="AF225" s="2" t="inlineStr"/>
+      <c r="AG225" s="2" t="inlineStr"/>
+      <c r="AH225" s="2" t="inlineStr"/>
+      <c r="AI225" s="2" t="inlineStr"/>
+      <c r="AJ225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>9422777761f044b4</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr"/>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>-0.24356469969969968</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:04.881694Z</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr"/>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
+      <c r="AB226" s="2" t="inlineStr"/>
+      <c r="AC226" s="2" t="inlineStr"/>
+      <c r="AD226" s="2" t="inlineStr"/>
+      <c r="AE226" s="2" t="inlineStr"/>
+      <c r="AF226" s="2" t="inlineStr"/>
+      <c r="AG226" s="2" t="inlineStr"/>
+      <c r="AH226" s="2" t="inlineStr"/>
+      <c r="AI226" s="2" t="inlineStr"/>
+      <c r="AJ226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>7d5a23a6ec59491d</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr"/>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>-0.12369693277310917</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:04.524904Z</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr"/>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
+      <c r="AB227" s="2" t="inlineStr"/>
+      <c r="AC227" s="2" t="inlineStr"/>
+      <c r="AD227" s="2" t="inlineStr"/>
+      <c r="AE227" s="2" t="inlineStr"/>
+      <c r="AF227" s="2" t="inlineStr"/>
+      <c r="AG227" s="2" t="inlineStr"/>
+      <c r="AH227" s="2" t="inlineStr"/>
+      <c r="AI227" s="2" t="inlineStr"/>
+      <c r="AJ227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>08e7f7099cf24497</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>0.03110723076923083</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:07:40.515562Z</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr"/>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
+      <c r="AB228" s="2" t="inlineStr"/>
+      <c r="AC228" s="2" t="inlineStr"/>
+      <c r="AD228" s="2" t="inlineStr"/>
+      <c r="AE228" s="2" t="inlineStr"/>
+      <c r="AF228" s="2" t="inlineStr"/>
+      <c r="AG228" s="2" t="inlineStr"/>
+      <c r="AH228" s="2" t="inlineStr"/>
+      <c r="AI228" s="2" t="inlineStr"/>
+      <c r="AJ228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>ce4deb5f81bc4204</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr"/>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>0.08085443192488262</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:07:40.102917Z</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr"/>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+      <c r="AB229" s="2" t="inlineStr"/>
+      <c r="AC229" s="2" t="inlineStr"/>
+      <c r="AD229" s="2" t="inlineStr"/>
+      <c r="AE229" s="2" t="inlineStr"/>
+      <c r="AF229" s="2" t="inlineStr"/>
+      <c r="AG229" s="2" t="inlineStr"/>
+      <c r="AH229" s="2" t="inlineStr"/>
+      <c r="AI229" s="2" t="inlineStr"/>
+      <c r="AJ229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>29f519739d804ad9</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr"/>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>-0.22437618210862614</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:07:40.108221Z</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr"/>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
+      <c r="AB230" s="2" t="inlineStr"/>
+      <c r="AC230" s="2" t="inlineStr"/>
+      <c r="AD230" s="2" t="inlineStr"/>
+      <c r="AE230" s="2" t="inlineStr"/>
+      <c r="AF230" s="2" t="inlineStr"/>
+      <c r="AG230" s="2" t="inlineStr"/>
+      <c r="AH230" s="2" t="inlineStr"/>
+      <c r="AI230" s="2" t="inlineStr"/>
+      <c r="AJ230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>a901fd2db2c44268</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr"/>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>-0.12369693277310917</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:07:39.806851Z</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr"/>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
+      <c r="AB231" s="2" t="inlineStr"/>
+      <c r="AC231" s="2" t="inlineStr"/>
+      <c r="AD231" s="2" t="inlineStr"/>
+      <c r="AE231" s="2" t="inlineStr"/>
+      <c r="AF231" s="2" t="inlineStr"/>
+      <c r="AG231" s="2" t="inlineStr"/>
+      <c r="AH231" s="2" t="inlineStr"/>
+      <c r="AI231" s="2" t="inlineStr"/>
+      <c r="AJ231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>0db6976a1cdd45f4</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr"/>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>0.03110723076923083</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:04.650923Z</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr"/>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
+      <c r="AB232" s="2" t="inlineStr"/>
+      <c r="AC232" s="2" t="inlineStr"/>
+      <c r="AD232" s="2" t="inlineStr"/>
+      <c r="AE232" s="2" t="inlineStr"/>
+      <c r="AF232" s="2" t="inlineStr"/>
+      <c r="AG232" s="2" t="inlineStr"/>
+      <c r="AH232" s="2" t="inlineStr"/>
+      <c r="AI232" s="2" t="inlineStr"/>
+      <c r="AJ232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>4cd3b70556c44dae</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>0.4694835680751174</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr"/>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>0.08085443192488262</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:04.399778Z</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr"/>
+      <c r="X233" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr"/>
+      <c r="AA233" s="2" t="inlineStr"/>
+      <c r="AB233" s="2" t="inlineStr"/>
+      <c r="AC233" s="2" t="inlineStr"/>
+      <c r="AD233" s="2" t="inlineStr"/>
+      <c r="AE233" s="2" t="inlineStr"/>
+      <c r="AF233" s="2" t="inlineStr"/>
+      <c r="AG233" s="2" t="inlineStr"/>
+      <c r="AH233" s="2" t="inlineStr"/>
+      <c r="AI233" s="2" t="inlineStr"/>
+      <c r="AJ233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>044ce8ade64e4e37</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr"/>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>-0.22437618210862614</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:04.488604Z</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr"/>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr"/>
+      <c r="AA234" s="2" t="inlineStr"/>
+      <c r="AB234" s="2" t="inlineStr"/>
+      <c r="AC234" s="2" t="inlineStr"/>
+      <c r="AD234" s="2" t="inlineStr"/>
+      <c r="AE234" s="2" t="inlineStr"/>
+      <c r="AF234" s="2" t="inlineStr"/>
+      <c r="AG234" s="2" t="inlineStr"/>
+      <c r="AH234" s="2" t="inlineStr"/>
+      <c r="AI234" s="2" t="inlineStr"/>
+      <c r="AJ234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>c63a28e97fbd4acf</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr"/>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>-0.12369693277310917</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:04.106538Z</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr"/>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr"/>
+      <c r="AA235" s="2" t="inlineStr"/>
+      <c r="AB235" s="2" t="inlineStr"/>
+      <c r="AC235" s="2" t="inlineStr"/>
+      <c r="AD235" s="2" t="inlineStr"/>
+      <c r="AE235" s="2" t="inlineStr"/>
+      <c r="AF235" s="2" t="inlineStr"/>
+      <c r="AG235" s="2" t="inlineStr"/>
+      <c r="AH235" s="2" t="inlineStr"/>
+      <c r="AI235" s="2" t="inlineStr"/>
+      <c r="AJ235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>7badb27075364148</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr"/>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>0.01982156807511737</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:12.406188Z</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr"/>
+      <c r="AA236" s="2" t="inlineStr"/>
+      <c r="AB236" s="2" t="inlineStr"/>
+      <c r="AC236" s="2" t="inlineStr"/>
+      <c r="AD236" s="2" t="inlineStr"/>
+      <c r="AE236" s="2" t="inlineStr"/>
+      <c r="AF236" s="2" t="inlineStr"/>
+      <c r="AG236" s="2" t="inlineStr"/>
+      <c r="AH236" s="2" t="inlineStr"/>
+      <c r="AI236" s="2" t="inlineStr"/>
+      <c r="AJ236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>d3ae0631a7764250</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr"/>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>0.060141921568627466</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:11.984077Z</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr"/>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr"/>
+      <c r="AB237" s="2" t="inlineStr"/>
+      <c r="AC237" s="2" t="inlineStr"/>
+      <c r="AD237" s="2" t="inlineStr"/>
+      <c r="AE237" s="2" t="inlineStr"/>
+      <c r="AF237" s="2" t="inlineStr"/>
+      <c r="AG237" s="2" t="inlineStr"/>
+      <c r="AH237" s="2" t="inlineStr"/>
+      <c r="AI237" s="2" t="inlineStr"/>
+      <c r="AJ237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>581b148afd874dd6</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr"/>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>-0.22437618210862614</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:12.269859Z</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr"/>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr"/>
+      <c r="AB238" s="2" t="inlineStr"/>
+      <c r="AC238" s="2" t="inlineStr"/>
+      <c r="AD238" s="2" t="inlineStr"/>
+      <c r="AE238" s="2" t="inlineStr"/>
+      <c r="AF238" s="2" t="inlineStr"/>
+      <c r="AG238" s="2" t="inlineStr"/>
+      <c r="AH238" s="2" t="inlineStr"/>
+      <c r="AI238" s="2" t="inlineStr"/>
+      <c r="AJ238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>1aa3c416a1f9497c</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr"/>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>-0.10333636563876653</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:11.868942Z</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr"/>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
+      <c r="AB239" s="2" t="inlineStr"/>
+      <c r="AC239" s="2" t="inlineStr"/>
+      <c r="AD239" s="2" t="inlineStr"/>
+      <c r="AE239" s="2" t="inlineStr"/>
+      <c r="AF239" s="2" t="inlineStr"/>
+      <c r="AG239" s="2" t="inlineStr"/>
+      <c r="AH239" s="2" t="inlineStr"/>
+      <c r="AI239" s="2" t="inlineStr"/>
+      <c r="AJ239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>1d586cfd7cb8431e</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr"/>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>0.03110723076923083</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:50.607001Z</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr"/>
+      <c r="W240" s="2" t="inlineStr"/>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr"/>
+      <c r="AB240" s="2" t="inlineStr"/>
+      <c r="AC240" s="2" t="inlineStr"/>
+      <c r="AD240" s="2" t="inlineStr"/>
+      <c r="AE240" s="2" t="inlineStr"/>
+      <c r="AF240" s="2" t="inlineStr"/>
+      <c r="AG240" s="2" t="inlineStr"/>
+      <c r="AH240" s="2" t="inlineStr"/>
+      <c r="AI240" s="2" t="inlineStr"/>
+      <c r="AJ240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>4f81f896d6ed4781</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr"/>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>0.159713</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:50.173250Z</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr"/>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
+      <c r="AB241" s="2" t="inlineStr"/>
+      <c r="AC241" s="2" t="inlineStr"/>
+      <c r="AD241" s="2" t="inlineStr"/>
+      <c r="AE241" s="2" t="inlineStr"/>
+      <c r="AF241" s="2" t="inlineStr"/>
+      <c r="AG241" s="2" t="inlineStr"/>
+      <c r="AH241" s="2" t="inlineStr"/>
+      <c r="AI241" s="2" t="inlineStr"/>
+      <c r="AJ241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>ee10fd9188ab47e8</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr"/>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>-0.2540099275362319</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:50.236946Z</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr"/>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr"/>
+      <c r="AB242" s="2" t="inlineStr"/>
+      <c r="AC242" s="2" t="inlineStr"/>
+      <c r="AD242" s="2" t="inlineStr"/>
+      <c r="AE242" s="2" t="inlineStr"/>
+      <c r="AF242" s="2" t="inlineStr"/>
+      <c r="AG242" s="2" t="inlineStr"/>
+      <c r="AH242" s="2" t="inlineStr"/>
+      <c r="AI242" s="2" t="inlineStr"/>
+      <c r="AJ242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>bd59a8b26a58410a</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr"/>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>-0.09341454954954947</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:50.024975Z</t>
+        </is>
+      </c>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr"/>
+      <c r="W243" s="2" t="inlineStr"/>
+      <c r="X243" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
+      <c r="AB243" s="2" t="inlineStr"/>
+      <c r="AC243" s="2" t="inlineStr"/>
+      <c r="AD243" s="2" t="inlineStr"/>
+      <c r="AE243" s="2" t="inlineStr"/>
+      <c r="AF243" s="2" t="inlineStr"/>
+      <c r="AG243" s="2" t="inlineStr"/>
+      <c r="AH243" s="2" t="inlineStr"/>
+      <c r="AI243" s="2" t="inlineStr"/>
+      <c r="AJ243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>bfc5b358484b4f1e</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>0.5192307692307692</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr"/>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0.03110723076923083</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.780496Z</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr"/>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr"/>
+      <c r="AB244" s="2" t="inlineStr"/>
+      <c r="AC244" s="2" t="inlineStr"/>
+      <c r="AD244" s="2" t="inlineStr"/>
+      <c r="AE244" s="2" t="inlineStr"/>
+      <c r="AF244" s="2" t="inlineStr"/>
+      <c r="AG244" s="2" t="inlineStr"/>
+      <c r="AH244" s="2" t="inlineStr"/>
+      <c r="AI244" s="2" t="inlineStr"/>
+      <c r="AJ244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>8f26e910c4b648ba</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>0.550338</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr"/>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>0.159713</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.118202Z</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr"/>
+      <c r="W245" s="2" t="inlineStr"/>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr"/>
+      <c r="AB245" s="2" t="inlineStr"/>
+      <c r="AC245" s="2" t="inlineStr"/>
+      <c r="AD245" s="2" t="inlineStr"/>
+      <c r="AE245" s="2" t="inlineStr"/>
+      <c r="AF245" s="2" t="inlineStr"/>
+      <c r="AG245" s="2" t="inlineStr"/>
+      <c r="AH245" s="2" t="inlineStr"/>
+      <c r="AI245" s="2" t="inlineStr"/>
+      <c r="AJ245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>3e05190031ad4a5f</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>401902572</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>0.7101449275362319</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr"/>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>-0.2540099275362319</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.664302Z</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr"/>
+      <c r="X246" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+      <c r="AB246" s="2" t="inlineStr"/>
+      <c r="AC246" s="2" t="inlineStr"/>
+      <c r="AD246" s="2" t="inlineStr"/>
+      <c r="AE246" s="2" t="inlineStr"/>
+      <c r="AF246" s="2" t="inlineStr"/>
+      <c r="AG246" s="2" t="inlineStr"/>
+      <c r="AH246" s="2" t="inlineStr"/>
+      <c r="AI246" s="2" t="inlineStr"/>
+      <c r="AJ246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>a23ad81637774d44</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>c95ec2023134439ab985cb4cdcc58243749b9deb564fca7a2d587c15c9875427</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>soccer-poisson-dc-v1</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>401902742</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>0.456135</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr"/>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>-0.09341454954954947</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:13:47.108429Z</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T22:00Z</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr"/>
+      <c r="W247" s="2" t="inlineStr"/>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
+      <c r="AB247" s="2" t="inlineStr"/>
+      <c r="AC247" s="2" t="inlineStr"/>
+      <c r="AD247" s="2" t="inlineStr"/>
+      <c r="AE247" s="2" t="inlineStr"/>
+      <c r="AF247" s="2" t="inlineStr"/>
+      <c r="AG247" s="2" t="inlineStr"/>
+      <c r="AH247" s="2" t="inlineStr"/>
+      <c r="AI247" s="2" t="inlineStr"/>
+      <c r="AJ247" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ217"/>
+  <autoFilter ref="A1:AJ247"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>